--- a/output/test-config/ActivitySoccer_preview.xlsx
+++ b/output/test-config/ActivitySoccer_preview.xlsx
@@ -37799,7 +37799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38395,7 +38395,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1001</v>
+        <v>10011</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1010</v>
+        <v>10101</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1010</v>
+        <v>10101</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -38554,53 +38554,33 @@
           <t>spotlight</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1010</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>drag</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>player_operate_area</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>player_drag_start</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>retry_step</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>trial_step</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>1011</v>
+        <v>10102</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -38609,13 +38589,13 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>试训1:进攻划线</t>
+          <t>试训1:进攻划线;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1011</v>
+        <v>10102</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -38624,7 +38604,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1011</t>
+          <t>ActvSoccer_guide_chapter_1010</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -38637,7 +38617,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>on_player_drag_start</t>
+          <t>on_trial_slice_enter</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -38646,19 +38626,11 @@
       <c r="H11" t="n">
         <v>101</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_1011</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bottom_bar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>predicted_trajectory</t>
+          <t>player_operate_area</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -38668,22 +38640,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1011</t>
+          <t>ActvSoccer_guide_gesture_1010</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>drag</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>target_goal_frame</t>
+          <t>player_operate_area</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>player_release_ball</t>
+          <t>player_drag_start</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -38691,12 +38663,28 @@
           <t>retry_step</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>trial_step</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
       <c r="V11" t="n">
-        <v>1012</v>
+        <v>10111</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -38705,13 +38693,13 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>试训1:松手射门</t>
+          <t>试训1:进攻划线;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1012</v>
+        <v>10111</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -38720,7 +38708,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1012</t>
+          <t>ActvSoccer_guide_chapter_1011</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -38733,7 +38721,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>on_slice_101_success</t>
+          <t>on_player_drag_start</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -38744,38 +38732,38 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1012</t>
+          <t>ActvSoccer_guide_dialogue_1011</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>toast</t>
+          <t>bottom_bar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>target_goal_frame</t>
+          <t>predicted_trajectory</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>spotlight</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>auto_delay</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>delay_end</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -38783,28 +38771,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>trial_step_1_done</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>1020</v>
+        <v>10112</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -38813,13 +38785,13 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>试训1成功</t>
+          <t>试训1:松手射门;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1013</v>
+        <v>10112</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -38828,7 +38800,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1013</t>
+          <t>ActvSoccer_guide_chapter_1011</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -38841,7 +38813,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>on_slice_101_fail</t>
+          <t>on_player_drag_start</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -38850,39 +38822,31 @@
       <c r="H13" t="n">
         <v>101</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_1013</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bottom_bar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
+          <t>predicted_trajectory</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_1011</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>release</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>target_goal_frame</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>spotlight</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1013</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>drag</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>player_operate_area</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -38900,7 +38864,7 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>1011</v>
+        <v>10121</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -38909,13 +38873,13 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>试训1失败重试</t>
+          <t>试训1:松手射门;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1020</v>
+        <v>10121</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -38924,7 +38888,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1020</t>
+          <t>ActvSoccer_guide_chapter_1012</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -38937,58 +38901,54 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>on_trial_slice_enter</t>
+          <t>on_slice_101_success</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1020</t>
+          <t>ActvSoccer_guide_dialogue_1012</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bottom_bar</t>
+          <t>toast</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>free_kick_target_area</t>
+          <t>target_goal_frame</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>spotlight</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1020</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>drag</t>
+          <t>auto_delay</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>power_angle_area</t>
+          <t>0.8s</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>player_drag_power</t>
+          <t>delay_end</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>retry_step</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -38998,12 +38958,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>trial_step</t>
+          <t>trial_step_1_done</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>true</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -39012,7 +38972,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1021</v>
+        <v>10201</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -39021,13 +38981,13 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>试训2:任意球方向和力度</t>
+          <t>试训1成功</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1021</v>
+        <v>10131</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -39036,7 +38996,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1021</t>
+          <t>ActvSoccer_guide_chapter_1013</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -39049,18 +39009,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>on_player_drag_power</t>
+          <t>on_slice_101_fail</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1021</t>
+          <t>ActvSoccer_guide_dialogue_1013</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -39070,7 +39030,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>power_percent_ui</t>
+          <t>target_goal_frame</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -39078,29 +39038,25 @@
           <t>spotlight</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1021</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>power_percent_ui</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>power_in_range_or_release</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>retry_step</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -39108,7 +39064,7 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>1022</v>
+        <v>10132</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -39117,13 +39073,13 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>试训2:力度教学</t>
+          <t>试训1失败重试;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1022</v>
+        <v>10132</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -39132,7 +39088,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1022</t>
+          <t>ActvSoccer_guide_chapter_1013</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -39145,78 +39101,58 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>on_slice_102_success</t>
+          <t>on_slice_101_fail</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>102</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_1022</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>toast</t>
-        </is>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>goal_target</t>
+          <t>target_goal_frame</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_1013</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>auto_delay</t>
+          <t>drag</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>player_operate_area</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>delay_end</t>
+          <t>player_release_ball</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>trial_step_2_done</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+          <t>retry_step</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>1030</v>
+        <v>10111</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -39225,13 +39161,13 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>试训2成功</t>
+          <t>试训1失败重试;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1023</v>
+        <v>10201</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -39240,7 +39176,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1023</t>
+          <t>ActvSoccer_guide_chapter_1020</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -39253,7 +39189,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>on_slice_102_fail_power_low</t>
+          <t>on_trial_slice_enter</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -39264,7 +39200,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1023</t>
+          <t>ActvSoccer_guide_dialogue_1020</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -39274,7 +39210,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>power_percent_ui</t>
+          <t>free_kick_target_area</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -39282,29 +39218,25 @@
           <t>spotlight</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1023</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>drag</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>power_angle_area</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>player_release_ball</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>retry_step</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -39312,7 +39244,7 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>1021</v>
+        <v>10202</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -39321,13 +39253,13 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>任意球力量太小</t>
+          <t>试训2:任意球方向和力度;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1024</v>
+        <v>10202</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -39336,7 +39268,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1024</t>
+          <t>ActvSoccer_guide_chapter_1020</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -39349,7 +39281,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>on_slice_102_fail_power_high</t>
+          <t>on_trial_slice_enter</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -39358,19 +39290,11 @@
       <c r="H18" t="n">
         <v>102</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_1024</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bottom_bar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>power_percent_ui</t>
+          <t>free_kick_target_area</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -39380,7 +39304,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1024</t>
+          <t>ActvSoccer_guide_gesture_1020</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -39395,7 +39319,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>player_release_ball</t>
+          <t>player_drag_power</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -39403,12 +39327,28 @@
           <t>retry_step</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>trial_step</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
       <c r="V18" t="n">
-        <v>1021</v>
+        <v>10211</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -39417,13 +39357,13 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>任意球力量太大</t>
+          <t>试训2:任意球方向和力度;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1025</v>
+        <v>10211</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -39432,7 +39372,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1025</t>
+          <t>ActvSoccer_guide_chapter_1021</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -39445,7 +39385,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>on_slice_102_fail_angle</t>
+          <t>on_player_drag_power</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -39456,7 +39396,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1025</t>
+          <t>ActvSoccer_guide_dialogue_1021</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -39466,7 +39406,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>angle_sector</t>
+          <t>power_percent_ui</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -39474,29 +39414,25 @@
           <t>spotlight</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1025</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>drag</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>power_angle_area</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>player_release_ball</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>retry_step</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -39504,7 +39440,7 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>1021</v>
+        <v>10212</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -39513,13 +39449,13 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>任意球角度偏离</t>
+          <t>试训2:力度教学;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1030</v>
+        <v>10212</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -39528,7 +39464,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1030</t>
+          <t>ActvSoccer_guide_chapter_1021</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -39541,28 +39477,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>on_trial_slice_enter</t>
+          <t>on_player_drag_power</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>103</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_1030</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bottom_bar</t>
-        </is>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>mode_toggle_button</t>
+          <t>power_percent_ui</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -39572,66 +39500,50 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1030</t>
+          <t>ActvSoccer_guide_gesture_1021</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>release</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>mode_toggle_button</t>
+          <t>power_percent_ui</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>mode_toggle_clicked_or_delay</t>
+          <t>power_in_range_or_release</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>trial_step</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+          <t>retry_step</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>1031</v>
+        <v>10221</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>auto_after_delay</t>
+          <t>cannot_skip</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>试训3:模式切换</t>
+          <t>试训2:力度教学;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1031</v>
+        <v>10221</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -39640,7 +39552,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1031</t>
+          <t>ActvSoccer_guide_chapter_1022</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -39653,66 +39565,78 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>on_mode_toggle_done</t>
+          <t>on_slice_102_success</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1031</t>
+          <t>ActvSoccer_guide_dialogue_1022</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bottom_bar</t>
+          <t>toast</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>penalty_goal_target</t>
+          <t>goal_target</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>spotlight</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1031</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>auto_delay</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>penalty_goal_target</t>
+          <t>0.8s</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>player_release_ball</t>
+          <t>delay_end</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>retry_step</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>trial_step_2_done</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
       <c r="V21" t="n">
-        <v>1032</v>
+        <v>10301</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -39721,13 +39645,13 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>试训3:点球射门</t>
+          <t>试训2成功</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1032</v>
+        <v>10231</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -39736,7 +39660,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1032</t>
+          <t>ActvSoccer_guide_chapter_1023</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -39749,49 +39673,49 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>on_slice_103_success</t>
+          <t>on_slice_102_fail_power_low</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1032</t>
+          <t>ActvSoccer_guide_dialogue_1023</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>toast</t>
+          <t>bottom_bar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>penalty_goal_target</t>
+          <t>power_percent_ui</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>spotlight</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>auto_delay</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.8s</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>delay_end</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -39799,28 +39723,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>trial_step_3_done</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>1040</v>
+        <v>10232</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -39829,13 +39737,13 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>试训3成功</t>
+          <t>任意球力量太小;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1033</v>
+        <v>10232</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -39844,7 +39752,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1033</t>
+          <t>ActvSoccer_guide_chapter_1023</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -39857,28 +39765,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>on_slice_103_fail</t>
+          <t>on_slice_102_fail_power_low</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>103</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_1033</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bottom_bar</t>
-        </is>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>penalty_goal_target</t>
+          <t>power_percent_ui</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -39888,17 +39788,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_1033</t>
+          <t>ActvSoccer_guide_gesture_1023</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>drag</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>penalty_goal_target</t>
+          <t>power_angle_area</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -39916,7 +39816,7 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>1031</v>
+        <v>10211</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -39925,13 +39825,13 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>点球失败重试</t>
+          <t>任意球力量太小;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1040</v>
+        <v>10241</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -39940,7 +39840,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_1040</t>
+          <t>ActvSoccer_guide_chapter_1024</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -39953,40 +39853,36 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>on_trial_all_slices_done</t>
+          <t>on_slice_102_fail_power_high</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_1040</t>
+          <t>ActvSoccer_guide_dialogue_1024</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>bottom_bar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>trial_complete_confirm</t>
+          <t>power_percent_ui</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_1040</t>
-        </is>
-      </c>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>tap</t>
@@ -39994,7 +39890,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>trial_complete_confirm</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -40007,28 +39903,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>trial_done</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>button_clicked</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>10242</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -40037,56 +39917,48 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>试训完成进入选队</t>
+          <t>任意球力量太大;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2001</v>
+        <v>10242</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>main_to_level1</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_2001</t>
+          <t>ActvSoccer_guide_chapter_1024</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>on_first_contract_signed</t>
+          <t>on_slice_102_fail_power_high</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_2001</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bubble</t>
-        </is>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>main_next_match_button</t>
+          <t>power_percent_ui</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -40096,51 +39968,35 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_2001</t>
+          <t>ActvSoccer_guide_gesture_1024</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>drag</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>main_next_match_button</t>
+          <t>power_angle_area</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>button_clicked</t>
+          <t>player_release_ball</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>main_guide_step</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>enter_level1</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+          <t>retry_step</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>2010</v>
+        <v>10211</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -40149,56 +40005,56 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>签约后强引导点下一场</t>
+          <t>任意球力量太大;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2010</v>
+        <v>10251</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>main_to_level1</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_2010</t>
+          <t>ActvSoccer_guide_chapter_1025</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>pre_battle</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>on_level1_prebattle_enter</t>
+          <t>on_slice_102_fail_angle</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_2010</t>
+          <t>ActvSoccer_guide_dialogue_1025</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bubble</t>
+          <t>bottom_bar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>level_goal_bar</t>
+          <t>angle_sector</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -40209,17 +40065,17 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>auto_delay</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.2s</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>delay_end</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -40227,28 +40083,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>main_guide_step</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>prebattle_goal_seen</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>2011</v>
+        <v>10252</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -40257,56 +40097,48 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>说明战前页目标条</t>
+          <t>任意球角度偏离;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2011</v>
+        <v>10252</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>main_to_level1</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_2011</t>
+          <t>ActvSoccer_guide_chapter_1025</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>pre_battle</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>after_goal_bar_tip</t>
+          <t>on_slice_102_fail_angle</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_2011</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bubble</t>
-        </is>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>kickoff_button</t>
+          <t>angle_sector</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -40316,51 +40148,35 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_2011</t>
+          <t>ActvSoccer_guide_gesture_1025</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>drag</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>kickoff_button</t>
+          <t>power_angle_area</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>button_clicked</t>
+          <t>player_release_ball</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>runtime</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>level1_attempt_started</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>button_clicked</t>
-        </is>
-      </c>
+          <t>retry_step</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>10211</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -40369,46 +40185,46 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>点击开球创建attempt</t>
+          <t>任意球角度偏离;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3001</v>
+        <v>10301</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3001</t>
+          <t>ActvSoccer_guide_chapter_1030</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>on_level1_attempt_started</t>
+          <t>on_trial_slice_enter</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3001</t>
+          <t>ActvSoccer_guide_dialogue_1030</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -40418,115 +40234,91 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>stadium_entry</t>
+          <t>mode_toggle_button</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>spotlight</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>entry_camera_end</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>runtime</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>guide_level_step</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>entry_done</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>3010</v>
+        <v>10302</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>cannot_skip</t>
+          <t>auto_after_delay</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>入场/开球/黑幕转切片</t>
+          <t>试训3:模式切换;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3010</v>
+        <v>10302</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3010</t>
+          <t>ActvSoccer_guide_chapter_1030</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>on_slice_201_enter</t>
+          <t>on_trial_slice_enter</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>201</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_3010</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bubble</t>
-        </is>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>controlled_player_ring</t>
+          <t>mode_toggle_button</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -40534,7 +40326,11 @@
           <t>spotlight</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_1030</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>tap</t>
@@ -40542,12 +40338,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>guide_confirm_button</t>
+          <t>mode_toggle_button</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>button_clicked</t>
+          <t>mode_toggle_clicked_or_delay</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -40557,17 +40353,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>runtime</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>guide_level_step</t>
+          <t>trial_step</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>201_player_focus_done</t>
+          <t>3</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -40576,65 +40372,65 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>3011</v>
+        <v>10311</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>cannot_skip</t>
+          <t>auto_after_delay</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>当前操作球员</t>
+          <t>试训3:模式切换;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3011</v>
+        <v>10311</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3011</t>
+          <t>ActvSoccer_guide_chapter_1031</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>after_player_ring_tip</t>
+          <t>on_mode_toggle_done</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3011</t>
+          <t>ActvSoccer_guide_dialogue_1031</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bubble</t>
+          <t>bottom_bar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>teammate_indicator</t>
+          <t>penalty_goal_target</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -40642,11 +40438,7 @@
           <t>spotlight</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3011</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>tap</t>
@@ -40667,28 +40459,12 @@
           <t>none</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>runtime</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>guide_level_step</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>201_teammate_indicator_done</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>3012</v>
+        <v>10312</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -40697,56 +40473,48 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>队友方向浮标</t>
+          <t>试训3:点球射门;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3012</v>
+        <v>10312</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3012</t>
+          <t>ActvSoccer_guide_chapter_1031</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>after_teammate_indicator_tip</t>
+          <t>on_mode_toggle_done</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>201</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_3012</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bottom_bar</t>
-        </is>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>camera_swipe_area</t>
+          <t>penalty_goal_target</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -40756,154 +40524,134 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3012</t>
+          <t>ActvSoccer_guide_gesture_1031</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>swipe</t>
+          <t>release</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>camera_swipe_area</t>
+          <t>penalty_goal_target</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>camera_swiped_or_delay</t>
+          <t>player_release_ball</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>runtime</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>guide_level_step</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>201_camera_done</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+          <t>retry_step</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>3013</v>
+        <v>10321</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>auto_after_delay</t>
+          <t>cannot_skip</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>视角滑动教学</t>
+          <t>试训3:点球射门;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3013</v>
+        <v>10321</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3013</t>
+          <t>ActvSoccer_guide_chapter_1032</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>after_camera_tip</t>
+          <t>on_slice_103_success</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3013</t>
+          <t>ActvSoccer_guide_dialogue_1032</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>bottom_bar</t>
+          <t>toast</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>slice_201_target</t>
+          <t>penalty_goal_target</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>spotlight</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3013</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>auto_delay</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>slice_201_target</t>
+          <t>0.8s</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>player_release_ball</t>
+          <t>delay_end</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>show_rewind</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>runtime</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>guide_level_step</t>
+          <t>trial_step_3_done</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>201_shoot_done</t>
+          <t>true</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -40912,7 +40660,7 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>3014</v>
+        <v>10401</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -40921,110 +40669,90 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>基础射门;首个非守门切片锁模式</t>
+          <t>试训3成功</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3014</v>
+        <v>10331</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3014</t>
+          <t>ActvSoccer_guide_chapter_1033</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>on_slice_201_success</t>
+          <t>on_slice_103_fail</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3014</t>
+          <t>ActvSoccer_guide_dialogue_1033</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>toast</t>
+          <t>bottom_bar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>replay_continue_button</t>
+          <t>penalty_goal_target</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3014</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>click_continue</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>replay_continue_button</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>button_clicked</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>attempt</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>slice_201_done</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>click_continue</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>3020</v>
+        <v>10332</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -41033,56 +40761,48 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>成功回放后继续</t>
+          <t>点球失败重试;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3015</v>
+        <v>10332</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3015</t>
+          <t>ActvSoccer_guide_chapter_1033</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>on_slice_201_fail</t>
+          <t>on_slice_103_fail</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>201</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_3015</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bubble</t>
-        </is>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>rewind_popup</t>
+          <t>penalty_goal_target</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -41092,51 +40812,35 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3015</t>
+          <t>ActvSoccer_guide_gesture_1033</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>release</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>rewind_free_button</t>
+          <t>penalty_goal_target</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>button_clicked</t>
+          <t>player_release_ball</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>continue_as_failed</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>rewind_tutorial_seen</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>button_clicked</t>
-        </is>
-      </c>
+          <t>retry_step</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>3013</v>
+        <v>10311</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -41145,110 +40849,90 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>第一次失败教回溯</t>
+          <t>点球失败重试;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3020</v>
+        <v>10401</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3020</t>
+          <t>ActvSoccer_guide_chapter_1040</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>on_slice_202_enter</t>
+          <t>on_trial_all_slices_done</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3020</t>
+          <t>ActvSoccer_guide_dialogue_1040</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>bottom_bar</t>
+          <t>popup</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teammate_target</t>
+          <t>trial_complete_confirm</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>spotlight</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3020</t>
-        </is>
-      </c>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>drag</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>teammate_target</t>
+          <t>guide_confirm_button</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>pass_released_to_teammate_area</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>show_rewind</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>runtime</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>guide_level_step</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>202_pass_prompt_done</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>step_complete</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>3021</v>
+        <v>10402</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -41257,106 +40941,102 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>助攻教学</t>
+          <t>试训完成进入选队;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3021</v>
+        <v>10402</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3021</t>
+          <t>ActvSoccer_guide_chapter_1040</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>trial</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>on_pass_to_teammate_success</t>
+          <t>on_trial_all_slices_done</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>202</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_3021</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bottom_bar</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teammate_shoot_target</t>
+          <t>trial_complete_confirm</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>spotlight</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_1040</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>trial_complete_confirm</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>teammate_shot_end</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>runtime</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>guide_level_step</t>
+          <t>trial_done</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>202_teammate_shot_seen</t>
+          <t>true</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>step_complete</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>3022</v>
+        <v>0</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -41365,110 +41045,90 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>队友自动射门表现</t>
+          <t>试训完成进入选队;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3022</v>
+        <v>20011</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>main_to_level1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3022</t>
+          <t>ActvSoccer_guide_chapter_2001</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>main</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>on_slice_202_success</t>
+          <t>on_first_contract_signed</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3022</t>
+          <t>ActvSoccer_guide_dialogue_2001</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>toast</t>
+          <t>bubble</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>replay_continue_button</t>
+          <t>main_next_match_button</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3022</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>click_continue</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>replay_continue_button</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>button_clicked</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>attempt</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>slice_202_done</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>click_continue</t>
-        </is>
-      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
-        <v>3030</v>
+        <v>20012</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -41477,56 +41137,48 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>助攻成功继续</t>
+          <t>签约后强引导点下一场;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3023</v>
+        <v>20012</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>main_to_level1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3023</t>
+          <t>ActvSoccer_guide_chapter_2001</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>main</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>on_slice_202_fail</t>
+          <t>on_first_contract_signed</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>202</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_3023</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bubble</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>rewind_popup</t>
+          <t>main_next_match_button</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -41536,7 +41188,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3023</t>
+          <t>ActvSoccer_guide_gesture_2001</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -41546,83 +41198,99 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>rewind_free_or_confirm_button</t>
+          <t>main_next_match_button</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>button_clicked_or_give_up</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>continue_as_failed</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>main_guide_step</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>enter_level1</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
       <c r="V38" t="n">
-        <v>3020</v>
+        <v>20101</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>allow_skip_if_seen</t>
+          <t>cannot_skip</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>助攻失败可回溯</t>
+          <t>签约后强引导点下一场;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3030</v>
+        <v>20101</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>main_to_level1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3030</t>
+          <t>ActvSoccer_guide_chapter_2010</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>pre_battle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>on_slice_203_enter</t>
+          <t>on_level1_prebattle_enter</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3030</t>
+          <t>ActvSoccer_guide_dialogue_2010</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>bottom_bar</t>
+          <t>bubble</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>goalkeeper</t>
+          <t>level_goal_bar</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -41630,44 +41298,40 @@
           <t>spotlight</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3030</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>swipe</t>
+          <t>auto_delay</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>save_direction_area</t>
+          <t>1.2s</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>goalkeep_swipe_finished</t>
+          <t>delay_end</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>show_rewind</t>
+          <t>none</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>runtime</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>guide_level_step</t>
+          <t>main_guide_step</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>203_goalkeep_prompt_done</t>
+          <t>prebattle_goal_seen</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -41676,7 +41340,7 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>3031</v>
+        <v>20111</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -41685,110 +41349,90 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>守门强制划线</t>
+          <t>说明战前页目标条</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3031</v>
+        <v>20111</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>main_to_level1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3031</t>
+          <t>ActvSoccer_guide_chapter_2011</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>pre_battle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>on_slice_203_success</t>
+          <t>after_goal_bar_tip</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3031</t>
+          <t>ActvSoccer_guide_dialogue_2011</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>toast</t>
+          <t>bubble</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>replay_continue_button</t>
+          <t>kickoff_button</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>none</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3031</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>click_continue</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>replay_continue_button</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>button_clicked</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>attempt</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>slice_203_done</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>click_continue</t>
-        </is>
-      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
-        <v>3040</v>
+        <v>20112</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -41797,56 +41441,48 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>守门成功继续</t>
+          <t>点击开球创建attempt;对话步骤</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3032</v>
+        <v>20112</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>level1_tutorial</t>
+          <t>main_to_level1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3032</t>
+          <t>ActvSoccer_guide_chapter_2011</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>pre_battle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>on_slice_203_fail</t>
+          <t>after_goal_bar_tip</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>203</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_dialogue_3032</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bubble</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>save_direction_area</t>
+          <t>kickoff_button</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -41856,50 +41492,66 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_gesture_3032</t>
+          <t>ActvSoccer_guide_gesture_2011</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>swipe</t>
+          <t>tap</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>save_direction_area</t>
+          <t>kickoff_button</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>goalkeep_swipe_finished_or_give_up</t>
+          <t>button_clicked</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>continue_as_failed</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>level1_attempt_started</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
       <c r="V41" t="n">
-        <v>3030</v>
+        <v>0</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>allow_skip_if_seen</t>
+          <t>cannot_skip</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>守门失败提示</t>
+          <t>点击开球创建attempt;手势/等待操作步骤</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3040</v>
+        <v>30011</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -41908,20 +41560,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_chapter_3040</t>
+          <t>ActvSoccer_guide_chapter_3001</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>level</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>on_level1_all_slices_done</t>
+          <t>on_level1_attempt_started</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -41932,42 +41584,38 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ActvSoccer_guide_dialogue_3040</t>
+          <t>ActvSoccer_guide_dialogue_3001</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>popup</t>
+          <t>bottom_bar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>level_settlement_confirm</t>
+          <t>stadium_entry</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>ActvSoccer_guide_gesture_3040</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>tap</t>
+          <t>none</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>level_settlement_confirm</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>button_clicked</t>
+          <t>entry_camera_end</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -41977,26 +41625,26 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>attempt</t>
+          <t>runtime</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>level1_settlement_confirmed</t>
+          <t>guide_level_step</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>entry_done</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>button_clicked</t>
+          <t>step_complete</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>3041</v>
+        <v>30101</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -42005,13 +41653,13 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>关卡结算确认</t>
+          <t>入场/开球/黑幕转切片</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3041</v>
+        <v>30101</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -42020,104 +41668,2724 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>ActvSoccer_guide_chapter_3010</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>on_slice_201_enter</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>201</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3010</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bubble</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>controlled_player_ring</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>guide_level_step</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>201_player_focus_done</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>30111</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>当前操作球员</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30111</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3011</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>after_player_ring_tip</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>201</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3011</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bubble</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teammate_indicator</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>30112</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>队友方向浮标;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>30112</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3011</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>after_player_ring_tip</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>201</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teammate_indicator</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3011</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>guide_level_step</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>201_teammate_indicator_done</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>30121</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>队友方向浮标;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>30121</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3012</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>after_teammate_indicator_tip</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>201</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3012</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bottom_bar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>camera_swipe_area</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>30122</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>auto_after_delay</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>视角滑动教学;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>30122</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3012</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>after_teammate_indicator_tip</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>201</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>camera_swipe_area</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3012</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>swipe</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>camera_swipe_area</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>camera_swiped_or_delay</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>guide_level_step</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>201_camera_done</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>30131</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>auto_after_delay</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>视角滑动教学;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>30131</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3013</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>after_camera_tip</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>201</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3013</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bottom_bar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>slice_201_target</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
+        <v>30132</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>基础射门;首个非守门切片锁模式;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>30132</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3013</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>after_camera_tip</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>201</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>slice_201_target</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3013</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>release</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>slice_201_target</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>player_release_ball</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>show_rewind</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>guide_level_step</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>201_shoot_done</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>30141</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>基础射门;首个非守门切片锁模式;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>30141</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3014</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>on_slice_201_success</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>201</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3014</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>toast</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="n">
+        <v>30142</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>成功回放后继续;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>30142</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3014</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>on_slice_201_success</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>201</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3014</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>click_continue</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>attempt</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>slice_201_done</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>click_continue</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>30201</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>成功回放后继续;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>30151</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3015</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>on_slice_201_fail</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>201</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3015</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bubble</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>rewind_popup</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="n">
+        <v>30152</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>第一次失败教回溯;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>30152</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3015</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>on_slice_201_fail</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>201</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>rewind_popup</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3015</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>rewind_free_button</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>continue_as_failed</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>rewind_tutorial_seen</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>30131</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>第一次失败教回溯;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>30201</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3020</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>on_slice_202_enter</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>202</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3020</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bottom_bar</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teammate_target</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>30202</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>助攻教学;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>30202</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3020</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>on_slice_202_enter</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>202</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teammate_target</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3020</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>drag</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>teammate_target</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>pass_released_to_teammate_area</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>show_rewind</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>guide_level_step</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>202_pass_prompt_done</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>30211</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>助攻教学;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>30211</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3021</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>on_pass_to_teammate_success</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
+        <v>202</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3021</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bottom_bar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teammate_shoot_target</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>teammate_shot_end</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>guide_level_step</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>202_teammate_shot_seen</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>30221</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>队友自动射门表现</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>30221</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3022</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>16</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>on_slice_202_success</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>202</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3022</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>toast</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="n">
+        <v>30222</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>助攻成功继续;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>30222</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3022</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>on_slice_202_success</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>202</v>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3022</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>click_continue</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>attempt</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>slice_202_done</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>click_continue</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>30301</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>助攻成功继续;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>30231</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3023</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>18</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>on_slice_202_fail</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>202</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3023</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bubble</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>rewind_popup</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="n">
+        <v>30232</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>allow_skip_if_seen</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>助攻失败可回溯;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>30232</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3023</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>19</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>on_slice_202_fail</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>202</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>rewind_popup</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3023</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>rewind_free_or_confirm_button</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>button_clicked_or_give_up</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>continue_as_failed</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
+        <v>30201</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>allow_skip_if_seen</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>助攻失败可回溯;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>30301</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3030</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>20</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>on_slice_203_enter</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>203</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3030</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bottom_bar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>goalkeeper</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
+        <v>30302</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>守门强制划线;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>30302</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3030</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>21</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>on_slice_203_enter</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>203</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>goalkeeper</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3030</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>swipe</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>save_direction_area</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>goalkeep_swipe_finished</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>show_rewind</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>guide_level_step</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>203_goalkeep_prompt_done</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>step_complete</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>30311</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>守门强制划线;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>30311</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3031</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>22</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>on_slice_203_success</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>203</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3031</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>toast</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="n">
+        <v>30312</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>守门成功继续;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30312</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3031</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>23</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>on_slice_203_success</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>203</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3031</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>click_continue</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>replay_continue_button</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>attempt</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>slice_203_done</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>click_continue</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>30401</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>守门成功继续;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>30321</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3032</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>24</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>on_slice_203_fail</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>203</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3032</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bubble</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>save_direction_area</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="n">
+        <v>30322</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>allow_skip_if_seen</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>守门失败提示;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>30322</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3032</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>25</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>on_slice_203_fail</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>203</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>save_direction_area</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>spotlight</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3032</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>swipe</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>save_direction_area</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>goalkeep_swipe_finished_or_give_up</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>continue_as_failed</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="n">
+        <v>30301</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>allow_skip_if_seen</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>守门失败提示;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>30401</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3040</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>26</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>on_level1_all_slices_done</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_dialogue_3040</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>popup</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>level_settlement_confirm</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="n">
+        <v>30402</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>关卡结算确认;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>30402</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3040</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>27</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>on_level1_all_slices_done</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>level_settlement_confirm</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_gesture_3040</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>level_settlement_confirm</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>attempt</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>level1_settlement_confirmed</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>30411</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>关卡结算确认;手势/等待操作步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>30411</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>ActvSoccer_guide_chapter_3041</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>16</v>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D69" t="n">
+        <v>28</v>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>settlement</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>on_rank_settlement_show</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>ActvSoccer_guide_dialogue_3041</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>popup</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>rank_settlement_confirm</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>tap</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>guide_confirm_button</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>button_clicked</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="n">
+        <v>30412</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>cannot_skip</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>排名确认，引导完成;对话步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>30412</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>level1_tutorial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ActvSoccer_guide_chapter_3041</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>29</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>on_rank_settlement_show</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>rank_settlement_confirm</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>ActvSoccer_guide_gesture_3041</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>tap</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>rank_settlement_confirm</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>button_clicked</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>profile</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>first_level_tutorial_done</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>button_clicked</t>
         </is>
       </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="inlineStr">
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="inlineStr">
         <is>
           <t>cannot_skip</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>排名确认，引导完成</t>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>排名确认，引导完成;手势/等待操作步骤</t>
         </is>
       </c>
     </row>

--- a/output/test-config/ActivitySoccer_preview.xlsx
+++ b/output/test-config/ActivitySoccer_preview.xlsx
@@ -39923,7 +39923,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>{"x": 11.661, "y": 0, "z": -12.633}</t>
+          <t>{"x": 11.7, "y": 0, "z": -12.6}</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>右路单刀；进攻射门基础站位；球点={"x": 11.661, "y": 0, "z": -12.633}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>右路单刀；进攻射门基础站位；球点={"x": 11.7, "y": 0, "z": -12.6}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -39999,7 +39999,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>{"x": -11.661, "y": 0, "z": -12.633}</t>
+          <t>{"x": -11.7, "y": 0, "z": -12.6}</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -40050,7 +40050,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>左路单刀；进攻射门基础站位；球点={"x": -11.661, "y": 0, "z": -12.633}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>左路单刀；进攻射门基础站位；球点={"x": -11.7, "y": 0, "z": -12.6}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -40227,7 +40227,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{"x": 0, "y": 0, "z": -16}</t>
+          <t>{"x": 0.0, "y": 0, "z": -15.5}</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -40240,7 +40240,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 0.0, "y": 0, "z": -16.5}, "facing": 0.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -11.0}, "facing": 149.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -11.0}, "facing": 163.3}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -11.0}, "facing": 180.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -11.0}, "facing": -163.3}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 0, "y": 0, "z": -16}, "facing": 0.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -11.0}, "facing": 149.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -11.0}, "facing": 163.3}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -11.0}, "facing": 180.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -11.0}, "facing": -163.3}]</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -40278,7 +40278,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>中路任意球；任意球+人墙基础站位；球点={"x": 0, "y": 0, "z": -16}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>中路任意球；任意球+人墙基础站位；球点={"x": 0.0, "y": 0, "z": -15.5}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -40303,7 +40303,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{"x": -10, "y": 0, "z": -14}</t>
+          <t>{"x": -9.7, "y": 0, "z": -13.6}</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -10.29, "y": 0, "z": -14.407}, "facing": 35.5}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -143.5}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -9.0}, "facing": -125.5}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -9.0}, "facing": -120.5}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -9.0}, "facing": -116.6}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -9.0}, "facing": -113.5}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -10, "y": 0, "z": -14}, "facing": 35.5}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -143.5}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -9.0}, "facing": -125.5}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -9.0}, "facing": -120.5}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -9.0}, "facing": -116.6}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -9.0}, "facing": -113.5}]</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -40354,7 +40354,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>左侧任意球；任意球+人墙基础站位；球点={"x": -10, "y": 0, "z": -14}；方向={"x":0,"y":0,"z":1}；目标={"x": -2, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>左侧任意球；任意球+人墙基础站位；球点={"x": -9.7, "y": 0, "z": -13.6}；方向={"x":0,"y":0,"z":1}；目标={"x": -2, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -40379,7 +40379,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>{"x": 10, "y": 0, "z": -14}</t>
+          <t>{"x": 9.7, "y": 0, "z": -13.6}</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -40392,7 +40392,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 10.29, "y": 0, "z": -14.407}, "facing": -35.5}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 143.5}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -9.0}, "facing": 111.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -9.0}, "facing": 113.5}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -9.0}, "facing": 116.6}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -9.0}, "facing": 120.5}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 10, "y": 0, "z": -14}, "facing": -35.5}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 143.5}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -9.0}, "facing": 111.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -9.0}, "facing": 113.5}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -9.0}, "facing": 116.6}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -9.0}, "facing": 120.5}]</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -40430,7 +40430,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>右侧任意球；任意球+人墙基础站位；球点={"x": 10, "y": 0, "z": -14}；方向={"x":0,"y":0,"z":1}；目标={"x": 2, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>右侧任意球；任意球+人墙基础站位；球点={"x": 9.7, "y": 0, "z": -13.6}；方向={"x":0,"y":0,"z":1}；目标={"x": 2, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -40455,7 +40455,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{"x": 4, "y": 0, "z": -17}</t>
+          <t>{"x": 3.9, "y": 0, "z": -16.5}</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -40468,7 +40468,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 4.114, "y": 0, "z": -17.487}, "facing": -13.2}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 166.4}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -12.0}, "facing": 125.5}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -12.0}, "facing": 132.3}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -12.0}, "facing": 141.3}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -12.0}, "facing": 153.4}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 4, "y": 0, "z": -17}, "facing": -13.2}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 166.4}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -12.0}, "facing": 125.5}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -12.0}, "facing": 132.3}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -12.0}, "facing": 141.3}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -12.0}, "facing": 153.4}]</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -40506,7 +40506,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>弧线任意球；任意球+人墙基础站位；球点={"x": 4, "y": 0, "z": -17}；方向={"x": -0.381, "y": 0, "z": 0.925}；目标={"x": -3, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>弧线任意球；任意球+人墙基础站位；球点={"x": 3.9, "y": 0, "z": -16.5}；方向={"x": -0.381, "y": 0, "z": 0.925}；目标={"x": -3, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -40696,7 +40696,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.499, "y": 0, "z": -1.03}, "facing": 86.6}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 2, "y": 0, "z": -6}, "facing": -75.3}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": -71.6}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0, "y": 0, "z": -8}, "facing": -67.6}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.5, "y": 0, "z": -1.0}, "facing": 86.6}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 2, "y": 0, "z": -6}, "facing": -75.3}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": -71.6}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0, "y": 0, "z": -8}, "facing": -67.6}]</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.499, "y": 0, "z": -1.03}, "facing": -86.6}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 2, "y": 0, "z": -6}, "facing": 71.6}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": 75.3}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0, "y": 0, "z": -8}, "facing": 67.6}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.5, "y": 0, "z": -1.0}, "facing": -86.6}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 2, "y": 0, "z": -6}, "facing": 71.6}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": 75.3}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0, "y": 0, "z": -8}, "facing": 67.6}]</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -40848,7 +40848,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.499, "y": 0, "z": -1.03}, "facing": -86.6}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 2, "y": 0, "z": -6}, "facing": 71.6}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": 75.3}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0, "y": 0, "z": -8}, "facing": 67.6}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.5, "y": 0, "z": -1.0}, "facing": -86.6}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 2, "y": 0, "z": -6}, "facing": 71.6}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": 75.3}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0, "y": 0, "z": -8}, "facing": 67.6}]</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -41291,7 +41291,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>{"x": 7.742, "y": 0, "z": -14.571}</t>
+          <t>{"x": 7.7, "y": 0, "z": -14.6}</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -41342,7 +41342,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>右肋斜插；进攻射门基础站位；球点={"x": 7.742, "y": 0, "z": -14.571}；方向={"x": -0.514, "y": 0, "z": 0.857}；目标={"x": -1, "y": 0.2, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>右肋斜插；进攻射门基础站位；球点={"x": 7.7, "y": 0, "z": -14.6}；方向={"x": -0.514, "y": 0, "z": 0.857}；目标={"x": -1, "y": 0.2, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41367,7 +41367,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>{"x": -7.742, "y": 0, "z": -14.571}</t>
+          <t>{"x": -7.7, "y": 0, "z": -14.6}</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -41418,7 +41418,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>左肋斜插；进攻射门基础站位；球点={"x": -7.742, "y": 0, "z": -14.571}；方向={"x": 0.514, "y": 0, "z": 0.857}；目标={"x": 1, "y": 0.2, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>左肋斜插；进攻射门基础站位；球点={"x": -7.7, "y": 0, "z": -14.6}；方向={"x": 0.514, "y": 0, "z": 0.857}；目标={"x": 1, "y": 0.2, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41519,7 +41519,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>{"x": 12.634, "y": 0, "z": -13.659}</t>
+          <t>{"x": 12.6, "y": 0, "z": -13.7}</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -41570,7 +41570,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>右路内切射门；进攻射门基础站位；球点={"x": 12.634, "y": 0, "z": -13.659}；方向={"x": -0.731, "y": 0, "z": 0.682}；目标={"x": -2, "y": 0.5, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>右路内切射门；进攻射门基础站位；球点={"x": 12.6, "y": 0, "z": -13.7}；方向={"x": -0.731, "y": 0, "z": 0.682}；目标={"x": -2, "y": 0.5, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41595,7 +41595,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"x": -12.634, "y": 0, "z": -13.659}</t>
+          <t>{"x": -12.6, "y": 0, "z": -13.7}</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -41646,7 +41646,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>左路内切射门；进攻射门基础站位；球点={"x": -12.634, "y": 0, "z": -13.659}；方向={"x": 0.731, "y": 0, "z": 0.682}；目标={"x": 2, "y": 0.5, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>左路内切射门；进攻射门基础站位；球点={"x": -12.6, "y": 0, "z": -13.7}；方向={"x": 0.731, "y": 0, "z": 0.682}；目标={"x": 2, "y": 0.5, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41671,7 +41671,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>{"x": 13.529, "y": 0, "z": -4.831}</t>
+          <t>{"x": 13.5, "y": 0, "z": -4.8}</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -41722,7 +41722,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>倒三角回做；进攻射门基础站位；球点={"x": 13.529, "y": 0, "z": -4.831}；方向={"x": -0.978, "y": 0, "z": -0.21}；目标={"x": 0, "y": 0, "z": -8}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>倒三角回做；进攻射门基础站位；球点={"x": 13.5, "y": 0, "z": -4.8}；方向={"x": -0.978, "y": 0, "z": -0.21}；目标={"x": 0, "y": 0, "z": -8}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41747,7 +41747,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>{"x": 2.824, "y": 0, "z": -7.532}</t>
+          <t>{"x": 2.8, "y": 0, "z": -7.5}</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -41798,7 +41798,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>门前抢点；进攻射门基础站位；球点={"x": 2.824, "y": 0, "z": -7.532}；方向={"x": -0.351, "y": 0, "z": 0.936}；目标={"x": 0, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>门前抢点；进攻射门基础站位；球点={"x": 2.8, "y": 0, "z": -7.5}；方向={"x": -0.351, "y": 0, "z": 0.936}；目标={"x": 0, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41823,7 +41823,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>{"x": -2.917, "y": 0, "z": -17.507}</t>
+          <t>{"x": -2.9, "y": 0, "z": -17.5}</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -41874,7 +41874,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>禁区外吊射；进攻射门基础站位；球点={"x": -2.917, "y": 0, "z": -17.507}；方向={"x": 0.164, "y": 0, "z": 0.986}；目标={"x": 0, "y": 2.2, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>禁区外吊射；进攻射门基础站位；球点={"x": -2.9, "y": 0, "z": -17.5}；方向={"x": 0.164, "y": 0, "z": 0.986}；目标={"x": 0, "y": 2.2, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41899,7 +41899,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>{"x": 4.675, "y": 0, "z": -6.62}</t>
+          <t>{"x": 4.7, "y": 0, "z": -6.6}</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -41950,7 +41950,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>二点补射；进攻射门基础站位；球点={"x": 4.675, "y": 0, "z": -6.62}；方向={"x": -0.651, "y": 0, "z": 0.759}；目标={"x": -1, "y": 0.6, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>二点补射；进攻射门基础站位；球点={"x": 4.7, "y": 0, "z": -6.6}；方向={"x": -0.651, "y": 0, "z": 0.759}；目标={"x": -1, "y": 0.6, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -41975,7 +41975,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>{"x": -4.803, "y": 0, "z": -13.54}</t>
+          <t>{"x": -4.8, "y": 0, "z": -13.5}</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>横向摆脱射门；进攻射门基础站位；球点={"x": -4.803, "y": 0, "z": -13.54}；方向={"x": 0.394, "y": 0, "z": 0.919}；目标={"x": 1, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>横向摆脱射门；进攻射门基础站位；球点={"x": -4.8, "y": 0, "z": -13.5}；方向={"x": 0.394, "y": 0, "z": 0.919}；目标={"x": 1, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -42051,7 +42051,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>{"x": 0, "y": 0, "z": -11}</t>
+          <t>{"x": 0.0, "y": 0, "z": -10.5}</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 0.0, "y": 0, "z": -11.5}, "facing": 0.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -7.0}, "facing": 143.1}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -7.0}, "facing": 159.4}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -7.0}, "facing": 180.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -7.0}, "facing": -159.4}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 0, "y": 0, "z": -11}, "facing": 0.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -7.0}, "facing": 143.1}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -7.0}, "facing": 159.4}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -7.0}, "facing": 180.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -7.0}, "facing": -159.4}]</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -42102,7 +42102,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>近距中路任意球；任意球+人墙基础站位；球点={"x": 0, "y": 0, "z": -11}；方向={"x": 0.0, "y": 0, "z": 1.0}；目标={"x": 0, "y": 1.6, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>近距中路任意球；任意球+人墙基础站位；球点={"x": 0.0, "y": 0, "z": -10.5}；方向={"x": 0.0, "y": 0, "z": 1.0}；目标={"x": 0, "y": 1.6, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -42127,7 +42127,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>{"x": 0, "y": 0, "z": -22}</t>
+          <t>{"x": 0.0, "y": 0, "z": -21.5}</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -42140,7 +42140,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 0.0, "y": 0, "z": -22.5}, "facing": 0.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -17.0}, "facing": 149.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -17.0}, "facing": 163.3}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -17.0}, "facing": 180.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -17.0}, "facing": -163.3}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 0, "y": 0, "z": -22}, "facing": 0.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -17.0}, "facing": 149.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -17.0}, "facing": 163.3}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -17.0}, "facing": 180.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -17.0}, "facing": -163.3}]</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -42178,7 +42178,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>远距中路任意球；任意球+人墙基础站位；球点={"x": 0, "y": 0, "z": -22}；方向={"x": 0.0, "y": 0, "z": 1.0}；目标={"x": 0, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>远距中路任意球；任意球+人墙基础站位；球点={"x": 0.0, "y": 0, "z": -21.5}；方向={"x": 0.0, "y": 0, "z": 1.0}；目标={"x": 0, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -42203,7 +42203,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>{"x": 8, "y": 0, "z": -15}</t>
+          <t>{"x": 7.8, "y": 0, "z": -14.6}</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -42216,7 +42216,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 8.236, "y": 0, "z": -15.441}, "facing": -28.1}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 151.1}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -10.0}, "facing": 114.4}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -10.0}, "facing": 117.8}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -10.0}, "facing": 122.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -10.0}, "facing": 127.6}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 8, "y": 0, "z": -15}, "facing": -28.1}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 151.1}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -10.0}, "facing": 114.4}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -10.0}, "facing": 117.8}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -10.0}, "facing": 122.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -10.0}, "facing": 127.6}]</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>右侧绕墙低射；任意球+人墙基础站位；球点={"x": 8, "y": 0, "z": -15}；方向={"x": -0.555, "y": 0, "z": 0.832}；目标={"x": -2, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>右侧绕墙低射；任意球+人墙基础站位；球点={"x": 7.8, "y": 0, "z": -14.6}；方向={"x": -0.555, "y": 0, "z": 0.832}；目标={"x": -2, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -42279,7 +42279,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>{"x": -8, "y": 0, "z": -15}</t>
+          <t>{"x": -7.8, "y": 0, "z": -14.6}</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -42292,7 +42292,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -8.236, "y": 0, "z": -15.441}, "facing": 28.1}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -151.1}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -10.0}, "facing": -135.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -10.0}, "facing": -127.6}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -10.0}, "facing": -122.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -10.0}, "facing": -117.8}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -8, "y": 0, "z": -15}, "facing": 28.1}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -151.1}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -10.0}, "facing": -135.0}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -10.0}, "facing": -127.6}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -10.0}, "facing": -122.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -10.0}, "facing": -117.8}]</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -42330,7 +42330,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>左侧绕墙低射；任意球+人墙基础站位；球点={"x": -8, "y": 0, "z": -15}；方向={"x": 0.555, "y": 0, "z": 0.832}；目标={"x": 2, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+          <t>左侧绕墙低射；任意球+人墙基础站位；球点={"x": -7.8, "y": 0, "z": -14.6}；方向={"x": 0.555, "y": 0, "z": 0.832}；目标={"x": 2, "y": 0.4, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -42355,7 +42355,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>{"x": 13, "y": 0, "z": -19}</t>
+          <t>{"x": 12.7, "y": 0, "z": -18.6}</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -42368,7 +42368,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 13.282, "y": 0, "z": -19.413}, "facing": -34.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 144.9}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -14.0}, "facing": 107.4}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -14.0}, "facing": 109.0}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -14.0}, "facing": 111.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -14.0}, "facing": 113.5}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 13, "y": 0, "z": -19}, "facing": -34.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 144.9}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -14.0}, "facing": 107.4}, {"team": "away", "idx": 2, "duty": 2, "pos": {"x": -1.5, "y": 0, "z": -14.0}, "facing": 109.0}, {"team": "away", "idx": 3, "duty": 2, "pos": {"x": 0.0, "y": 0, "z": -14.0}, "facing": 111.0}, {"team": "away", "idx": 4, "duty": 2, "pos": {"x": 1.5, "y": 0, "z": -14.0}, "facing": 113.5}]</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -42406,7 +42406,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>传中任意球；任意球+人墙基础站位；球点={"x": 13, "y": 0, "z": -19}；方向={"x": -0.644, "y": 0, "z": 0.765}；目标={"x": -3, "y": 2.2, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>传中任意球；任意球+人墙基础站位；球点={"x": 12.7, "y": 0, "z": -18.6}；方向={"x": -0.644, "y": 0, "z": 0.765}；目标={"x": -3, "y": 2.2, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -42672,7 +42672,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.498, "y": 0, "z": -1.042}, "facing": 85.2}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -5, "y": 0, "z": -6}, "facing": -67.4}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 5, "y": 0, "z": -7}, "facing": -74.7}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -2.5, "y": 0, "z": -8}, "facing": -64.2}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.5, "y": 0, "z": -1.0}, "facing": 85.2}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -5, "y": 0, "z": -6}, "facing": -67.4}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 5, "y": 0, "z": -7}, "facing": -74.7}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -2.5, "y": 0, "z": -8}, "facing": -64.2}]</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -42748,7 +42748,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.498, "y": 0, "z": -1.042}, "facing": -85.2}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 5, "y": 0, "z": -6}, "facing": 67.4}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -5, "y": 0, "z": -7}, "facing": 74.7}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 2.5, "y": 0, "z": -8}, "facing": 64.2}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.5, "y": 0, "z": -1.0}, "facing": -85.2}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 5, "y": 0, "z": -6}, "facing": 67.4}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -5, "y": 0, "z": -7}, "facing": 74.7}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 2.5, "y": 0, "z": -8}, "facing": 64.2}]</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -42824,7 +42824,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.5, "y": 0, "z": -1.022}, "facing": 87.5}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 6, "y": 0, "z": -6}, "facing": -77.7}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -6, "y": 0, "z": -7}, "facing": -61.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 3.0, "y": 0, "z": -8}, "facing": -70.7}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.5, "y": 0, "z": -1.0}, "facing": 87.5}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 6, "y": 0, "z": -6}, "facing": -77.7}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -6, "y": 0, "z": -7}, "facing": -61.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 3.0, "y": 0, "z": -8}, "facing": -70.7}]</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -42900,7 +42900,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.5, "y": 0, "z": -1.022}, "facing": -87.5}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -6, "y": 0, "z": -6}, "facing": 77.7}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 6, "y": 0, "z": -7}, "facing": 61.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -8}, "facing": 70.7}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.5, "y": 0, "z": -1.0}, "facing": -87.5}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -6, "y": 0, "z": -6}, "facing": 77.7}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 6, "y": 0, "z": -7}, "facing": 61.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -3.0, "y": 0, "z": -8}, "facing": 70.7}]</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -42976,7 +42976,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.354, "y": 0, "z": -0.646}, "facing": 135.0}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -12, "y": 0, "z": -6}, "facing": -45.0}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 12, "y": 0, "z": -7}, "facing": -78.3}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -6.0, "y": 0, "z": -8}, "facing": -57.5}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.4, "y": 0, "z": -0.6}, "facing": 135.0}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -12, "y": 0, "z": -6}, "facing": -45.0}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 12, "y": 0, "z": -7}, "facing": -78.3}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -6.0, "y": 0, "z": -8}, "facing": -57.5}]</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -43052,7 +43052,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.499, "y": 0, "z": -0.974}, "facing": -93.0}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": 75.3}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 2, "y": 0, "z": -7}, "facing": 68.2}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -1.0, "y": 0, "z": -8}, "facing": 68.7}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 17.5, "y": 0, "z": -1.0}, "facing": -93.0}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -2, "y": 0, "z": -6}, "facing": 75.3}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": 2, "y": 0, "z": -7}, "facing": 68.2}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": 91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -1.0, "y": 0, "z": -8}, "facing": 68.7}]</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -43128,7 +43128,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.488, "y": 0, "z": -0.892}, "facing": 102.5}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 1, "y": 0, "z": -6}, "facing": -74.5}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -1, "y": 0, "z": -7}, "facing": -69.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0.5, "y": 0, "z": -8}, "facing": -68.2}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -17.5, "y": 0, "z": -0.9}, "facing": 102.5}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 1, "y": 0, "z": -6}, "facing": -74.5}, {"team": "home", "idx": 2, "duty": 3, "pos": {"x": -1, "y": 0, "z": -7}, "facing": -69.4}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -0.5}, "facing": -91.7}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 0.5, "y": 0, "z": -8}, "facing": -68.2}]</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -43191,7 +43191,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>{"x": -17.526, "y": 0, "z": -9.842}</t>
+          <t>{"x": -17.5, "y": 0, "z": -9.8}</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -43242,7 +43242,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>左侧近端接应；界外球二次进攻基础站位；球点={"x": -17.526, "y": 0, "z": -9.842}；方向={"x": 0.949, "y": 0, "z": 0.316}；目标={"x": -12, "y": 0, "z": -8}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>左侧近端接应；界外球二次进攻基础站位；球点={"x": -17.5, "y": 0, "z": -9.8}；方向={"x": 0.949, "y": 0, "z": 0.316}；目标={"x": -12, "y": 0, "z": -8}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43267,7 +43267,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>{"x": 17.526, "y": 0, "z": -9.842}</t>
+          <t>{"x": 17.5, "y": 0, "z": -9.8}</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>右侧近端接应；界外球二次进攻基础站位；球点={"x": 17.526, "y": 0, "z": -9.842}；方向={"x": -0.949, "y": 0, "z": 0.316}；目标={"x": 12, "y": 0, "z": -8}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>右侧近端接应；界外球二次进攻基础站位；球点={"x": 17.5, "y": 0, "z": -9.8}；方向={"x": -0.949, "y": 0, "z": 0.316}；目标={"x": 12, "y": 0, "z": -8}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43343,7 +43343,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>{"x": -17.522, "y": 0, "z": -22.855}</t>
+          <t>{"x": -17.5, "y": 0, "z": -22.9}</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -43394,7 +43394,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>左侧远端转移；界外球二次进攻基础站位；球点={"x": -17.522, "y": 0, "z": -22.855}；方向={"x": 0.957, "y": 0, "z": 0.291}；目标={"x": 5, "y": 0, "z": -16}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>左侧远端转移；界外球二次进攻基础站位；球点={"x": -17.5, "y": 0, "z": -22.9}；方向={"x": 0.957, "y": 0, "z": 0.291}；目标={"x": 5, "y": 0, "z": -16}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43419,7 +43419,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>{"x": 17.522, "y": 0, "z": -22.855}</t>
+          <t>{"x": 17.5, "y": 0, "z": -22.9}</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -43470,7 +43470,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>右侧远端转移；界外球二次进攻基础站位；球点={"x": 17.522, "y": 0, "z": -22.855}；方向={"x": -0.957, "y": 0, "z": 0.291}；目标={"x": -5, "y": 0, "z": -16}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>右侧远端转移；界外球二次进攻基础站位；球点={"x": 17.5, "y": 0, "z": -22.9}；方向={"x": -0.957, "y": 0, "z": 0.291}；目标={"x": -5, "y": 0, "z": -16}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43495,7 +43495,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>{"x": -17.59, "y": 0, "z": -24.713}</t>
+          <t>{"x": -17.6, "y": 0, "z": -24.7}</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -43546,7 +43546,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>左路快速反击；界外球二次进攻基础站位；球点={"x": -17.59, "y": 0, "z": -24.713}；方向={"x": 0.819, "y": 0, "z": 0.573}；目标={"x": -8, "y": 0, "z": -18}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>左路快速反击；界外球二次进攻基础站位；球点={"x": -17.6, "y": 0, "z": -24.7}；方向={"x": 0.819, "y": 0, "z": 0.573}；目标={"x": -8, "y": 0, "z": -18}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>{"x": 17.59, "y": 0, "z": -24.713}</t>
+          <t>{"x": 17.6, "y": 0, "z": -24.7}</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>右路快速反击；界外球二次进攻基础站位；球点={"x": 17.59, "y": 0, "z": -24.713}；方向={"x": -0.819, "y": 0, "z": 0.573}；目标={"x": 8, "y": 0, "z": -18}；控球home[0]；推荐操作=["draw_line"]</t>
+          <t>右路快速反击；界外球二次进攻基础站位；球点={"x": 17.6, "y": 0, "z": -24.7}；方向={"x": -0.819, "y": 0, "z": 0.573}；目标={"x": 8, "y": 0, "z": -18}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
